--- a/output/pdf_financials_xlsx/GVC.xlsx
+++ b/output/pdf_financials_xlsx/GVC.xlsx
@@ -1633,19 +1633,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>7.931</v>
+        <v>12.434</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>7.073</v>
+        <v>12.748</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>8.048999999999999</v>
+        <v>13.453</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>6.742</v>
+        <v>11.402</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>7.868</v>
+        <v>11.996</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>11.463</v>
@@ -1676,19 +1676,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-56.501</v>
+        <v>-51.998</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>17.423</v>
+        <v>23.098</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-179.162</v>
+        <v>-173.758</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>8.865</v>
+        <v>13.525</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7.245</v>
+        <v>11.373</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>12.112</v>
@@ -1719,19 +1719,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-21.55383212723021</v>
+        <v>-19.83604118425721</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>7.029059470450355</v>
+        <v>9.318556829963972</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-81.17824034218086</v>
+        <v>-78.72968980797637</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>4.459434987323434</v>
+        <v>6.803593705984144</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.789800754298508</v>
+        <v>5.949124082627595</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>6.429830335718684</v>
@@ -4687,19 +4687,19 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>13.886</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>12.748</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>13.453</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>11.402</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>11.996</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>11.463</v>
@@ -25170,7 +25170,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E260" s="5" t="n">
         <v>5.955</v>
       </c>
@@ -25238,7 +25242,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E261" s="5" t="n">
@@ -37688,7 +37692,11 @@
           <t>Depreciation of property, plant and equipment (Note 11)</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -37760,7 +37768,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -39906,7 +39914,11 @@
           <t>Depreciation of property, plant and equipment (Note 12)</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E458" s="5" t="n">
         <v>5.882</v>
       </c>
@@ -39980,7 +39992,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E459" s="5" t="n">

--- a/output/pdf_financials_xlsx/GVC.xlsx
+++ b/output/pdf_financials_xlsx/GVC.xlsx
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>2.798</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>2.055</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>0</v>
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>56.212</v>
+        <v>59.01</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>49.403</v>
+        <v>51.458</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>39.817</v>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.487</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>26.567</v>
+        <v>24.512</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>2.554</v>
@@ -3298,40 +3298,40 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>23.867</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>22.655</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>21.795</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>24.216</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>24.011</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>22.747</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>23.274</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>22.611</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>23.163</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>26.491</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>24.226</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>22.558</v>
       </c>
     </row>
     <row r="68">
@@ -3341,40 +3341,40 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>33.987</v>
+        <v>57.854</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>30.737</v>
+        <v>53.392</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>29.106</v>
+        <v>50.901</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>27.738</v>
+        <v>51.954</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>25.021</v>
+        <v>49.032</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>25.671</v>
+        <v>48.418</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>25.738</v>
+        <v>49.012</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>29.624</v>
+        <v>52.235</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>29.515</v>
+        <v>52.678</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>27.671</v>
+        <v>54.162</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>25.025</v>
+        <v>49.251</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>23.183</v>
+        <v>45.741</v>
       </c>
     </row>
     <row r="69">
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>2.978</v>
       </c>
       <c r="K107" s="3" t="n">
         <v>0.5639999999999999</v>
@@ -5375,40 +5375,40 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-2.204</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-2.523</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-2.17</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-1.911</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-2.954</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-3.999</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-4.076</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-3.333</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-3.238</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-2.548</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-3.458</v>
       </c>
     </row>
     <row r="117">
@@ -5503,40 +5503,26 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>3.416</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>8.249000000000001</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>5.552</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>2.121</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>1.658</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>-1.964</v>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>18.666</v>
       </c>
       <c r="I119" s="3" t="n">
         <v>-0.342</v>
@@ -5544,20 +5530,14 @@
       <c r="J119" s="3" t="n">
         <v>-2.77</v>
       </c>
-      <c r="K119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K119" s="3" t="n">
+        <v>-1.489</v>
+      </c>
+      <c r="L119" s="3" t="n">
+        <v>3.524</v>
+      </c>
+      <c r="M119" s="3" t="n">
+        <v>-2.751</v>
       </c>
     </row>
     <row r="120">
@@ -5610,7 +5590,7 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -5634,10 +5614,10 @@
         <v>0</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-0.432</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-0.168</v>
       </c>
       <c r="L121" s="3" t="n">
         <v>0</v>
@@ -6235,40 +6215,26 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>24.808</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>23.795</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>9.768000000000001</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>9.832000000000001</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>4.387</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>-1.552</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>8.622999999999999</v>
@@ -6276,20 +6242,14 @@
       <c r="J135" s="3" t="n">
         <v>6.334</v>
       </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K135" s="3" t="n">
+        <v>-7.62</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="M135" s="3" t="n">
+        <v>2.341</v>
       </c>
     </row>
   </sheetData>
@@ -18548,7 +18508,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -18978,7 +18942,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -20136,7 +20104,11 @@
           <t>Deferred income tax recovery (Note 23)</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -20512,7 +20484,11 @@
           <t>Cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -20736,7 +20712,11 @@
           <t>Purchase of intangible assets (Note 11)</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -20880,7 +20860,11 @@
           <t>Repurchase of commons shares</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -21260,7 +21244,11 @@
           <t>Deferred income tax recovery (Note 23)</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -21482,7 +21470,11 @@
           <t>Share-based compensation expenses (Note 25 c)</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -22026,7 +22018,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -22540,7 +22536,11 @@
           <t>Purchase of intangible assets (Note 11)</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -22844,7 +22844,11 @@
           <t>Repurchase of commons shares (Note 20)</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -23518,7 +23522,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -24412,7 +24420,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -26094,7 +26106,11 @@
           <t>Purchase of intangible assets (Note 12)</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -27132,7 +27148,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E287" s="5" t="n">
         <v>-61.829</v>
       </c>
@@ -27350,7 +27370,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -28092,7 +28116,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -28544,7 +28572,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E306" s="5" t="n">
         <v>34.341</v>
       </c>
@@ -29218,7 +29250,11 @@
           <t>Deferred income taxes (recovery)</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E315" s="5" t="n">
         <v>-9.907999999999999</v>
       </c>
@@ -30340,7 +30376,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E330" s="5" t="n">
         <v>-2.204</v>
       </c>
@@ -30720,7 +30760,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E335" s="5" t="n">
         <v>-0.25</v>
       </c>
@@ -32002,7 +32046,11 @@
           <t>Income tax recovery (Note 23)</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
@@ -33800,7 +33848,11 @@
           <t>Income tax (recovery) expense (Note 23)</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -35216,7 +35268,11 @@
           <t>Income tax recovery (Note 23)</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -37086,7 +37142,11 @@
           <t>Income tax recovery (Note 24)</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -38128,7 +38188,11 @@
           <t>Income tax recovery (Note 19 and 23)</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -38942,7 +39006,11 @@
           <t>Income tax recovery (Note 18 and 22)</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
           <t>-</t>
@@ -39542,7 +39610,11 @@
           <t>Income tax recovery (Notes 18 and 22)</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
           <t>-</t>
@@ -40438,7 +40510,11 @@
           <t>Income tax (recovery) expense (Notes 19 and 23)</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E465" t="inlineStr">
         <is>
           <t>-</t>
